--- a/artfynd/A 4779-2025 artfynd.xlsx
+++ b/artfynd/A 4779-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2680,6 +2680,114 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122788734</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56437</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>327621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6351154</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4779-2025 artfynd.xlsx
+++ b/artfynd/A 4779-2025 artfynd.xlsx
@@ -2685,7 +2685,7 @@
         <v>122788734</v>
       </c>
       <c r="B17" t="n">
-        <v>56437</v>
+        <v>56440</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 4779-2025 artfynd.xlsx
+++ b/artfynd/A 4779-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16824158</v>
+        <v>114315821</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingome, Hl</t>
+          <t>Bua, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327506.6103221808</v>
+        <v>327707</v>
       </c>
       <c r="R2" t="n">
-        <v>6351190.630425301</v>
+        <v>6350856</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Trol honbo i björbärssnår. 10 cm och 120 cm över mark.</t>
+          <t>Fynd rapporterad efter NVI utförd vid Bua av Calluna AB oktober-november 2023</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,31 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Ringhals NVI</t>
+          <t>Calluna AB: NVI JMN0117 Bua 2023</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16824159</v>
+        <v>16822074</v>
       </c>
       <c r="B3" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -856,14 +829,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingome, Hl</t>
+          <t>Lingome 18:1&gt;4 Mellersta, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327503.8121902103</v>
+        <v>327600</v>
       </c>
       <c r="R3" t="n">
-        <v>6351188.582684408</v>
+        <v>6351018</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,27 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hanbo i björnbärssnår. 7 cm och 90 cm över marken.</t>
+          <t>Litet bo. Juvenil? 6-7 cm. Placerat i björbärssnår ca 80 cm över mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,12 +888,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -941,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16824163</v>
+        <v>16824158</v>
       </c>
       <c r="B4" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327642.7165373018</v>
+        <v>327507</v>
       </c>
       <c r="R4" t="n">
-        <v>6351267.194078147</v>
+        <v>6351191</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,24 +984,14 @@
           <t>2014-11-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-11-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hanbo i liten ek i bjärnbärssnår. 7 cm och 120 cm över marken</t>
+          <t>Trol honbo i björbärssnår. 10 cm och 120 cm över mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,12 +1006,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1074,15 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95751366</v>
+        <v>16824159</v>
       </c>
       <c r="B5" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>100084</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,24 +1055,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkulla, Hl</t>
+          <t>Lingome, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327658.7647304349</v>
+        <v>327504</v>
       </c>
       <c r="R5" t="n">
-        <v>6351029.410298335</v>
+        <v>6351189</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,22 +1099,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hanbo i björnbärssnår. 7 cm och 90 cm över marken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,34 +1118,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Mikael Hellman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98719828</v>
+        <v>16824163</v>
       </c>
       <c r="B6" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,35 +1173,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vä 26, Hl</t>
+          <t>Lingome, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327522.9146257306</v>
+        <v>327643</v>
       </c>
       <c r="R6" t="n">
-        <v>6351165.584556445</v>
+        <v>6351267</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1286,27 +1217,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Yngelbo 11,5 cm. Boplats 1,5 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
+          <t>Hanbo i liten ek i bjärnbärssnår. 7 cm och 120 cm över marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,27 +1242,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Mikael Hellman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Boris Berglund, Tage Vowles</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Mikael Hellman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98720169</v>
+        <v>98719361</v>
       </c>
       <c r="B7" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1298,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1389,14 +1309,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vä 31, Hl</t>
+          <t>Vä 22, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327659.861102894</v>
+        <v>327525</v>
       </c>
       <c r="R7" t="n">
-        <v>6351262.143279788</v>
+        <v>6351164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1426,24 +1346,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hanbo 7 cm. Boplats 0,8 m över marken i ek. Sydvästbryn med björnbärssnår och 1,5-2 m höga småekar.  Överståndare av björk.</t>
+          <t>Yngelbo 14 x 11 cm. Boplats 0.40 m över marken i björnbär. "Schichnest" med ytterhöljet byggt av mer eller mindre hela blad. Tydlig kärna av finrispat gräs. Habitatet utgöres av björnbärssnår med inslag av kaprifol. Överståndare av björk och ek.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1470,15 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98719988</v>
+        <v>98719494</v>
       </c>
       <c r="B8" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1420,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1526,14 +1431,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vä 29, Hl</t>
+          <t>Vä 23, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327594.1789569597</v>
+        <v>327525</v>
       </c>
       <c r="R8" t="n">
-        <v>6351144.725194343</v>
+        <v>6351169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1563,24 +1468,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Yngelbo 10 cm. Boplats 1,7 m över marken i ek. Samma fina ekkrattskog som föregående med rikligt inslag av kaprifol.</t>
+          <t>Hanbo under pågående sönderfall, c:a 7 cm. Boplats 0,5 m över marken i björnbärssnår. Samma björnbärssnår som föregående. Även tall som överståndare.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1607,15 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98719494</v>
+        <v>98719578</v>
       </c>
       <c r="B9" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1542,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1663,14 +1553,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vä 23, Hl</t>
+          <t>Vä 24, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>327525.2167364248</v>
+        <v>327525</v>
       </c>
       <c r="R9" t="n">
-        <v>6351168.735862822</v>
+        <v>6351174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1700,24 +1590,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hanbo under pågående sönderfall, c:a 7 cm. Boplats 0,5 m över marken i björnbärssnår. Samma björnbärssnår som föregående. Även tall som överståndare.</t>
+          <t>Yngelbo 12 cm. Boplats 0,8 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1744,15 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98719945</v>
+        <v>98719710</v>
       </c>
       <c r="B10" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1789,7 +1664,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1800,14 +1675,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vä 28, Hl</t>
+          <t>Vä 25, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327582.691289882</v>
+        <v>327523</v>
       </c>
       <c r="R10" t="n">
-        <v>6351129.508771866</v>
+        <v>6351170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1837,24 +1712,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Yngelbo 10 cm. Boplats 1,5 m över marken i ek. Samma ekkrattskog som föregående. Mycket rikligt inslag av kaprifol. Fint hasselmushabitat.</t>
+          <t>Hanbo c:a 7 cm. Boplats 0,9 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,15 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98719361</v>
+        <v>98719828</v>
       </c>
       <c r="B11" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,14 +1797,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vä 22, Hl</t>
+          <t>Vä 26, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327525.0123041218</v>
+        <v>327523</v>
       </c>
       <c r="R11" t="n">
-        <v>6351163.872344722</v>
+        <v>6351166</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1974,24 +1834,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Yngelbo 14 x 11 cm. Boplats 0.40 m över marken i björnbär. "Schichnest" med ytterhöljet byggt av mer eller mindre hela blad. Tydlig kärna av finrispat gräs. Habitatet utgöres av björnbärssnår med inslag av kaprifol. Överståndare av björk och ek.</t>
+          <t>Yngelbo 11,5 cm. Boplats 1,5 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2018,15 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98719710</v>
+        <v>98719918</v>
       </c>
       <c r="B12" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2074,14 +1919,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vä 25, Hl</t>
+          <t>Vä 27, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327523.0963455824</v>
+        <v>327566</v>
       </c>
       <c r="R12" t="n">
-        <v>6351169.907682169</v>
+        <v>6351137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2111,24 +1956,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hanbo c:a 7 cm. Boplats 0,9 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
+          <t>Hanbo 7 cm. Boplats 1,5 m över marken i ek med rikligt  inslag av kaprifol. Ung krattskog av ek, 2-3 m hög. En del närliggande överståndare av björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2155,15 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98719578</v>
+        <v>98719945</v>
       </c>
       <c r="B13" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2211,14 +2041,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vä 24, Hl</t>
+          <t>Vä 28, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>327524.879714027</v>
+        <v>327582</v>
       </c>
       <c r="R13" t="n">
-        <v>6351173.622134634</v>
+        <v>6351129</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2248,24 +2078,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Yngelbo 12 cm. Boplats 0,8 m över marken i björnbär. Samma björnbärssnår som föregående.</t>
+          <t>Yngelbo 10 cm. Boplats 1,5 m över marken i ek. Samma ekkrattskog som föregående. Mycket rikligt inslag av kaprifol. Fint hasselmushabitat.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2292,15 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98720044</v>
+        <v>98719988</v>
       </c>
       <c r="B14" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2348,14 +2163,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vä 30, Hl</t>
+          <t>Vä 29, Hl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>327602.3462393211</v>
+        <v>327594</v>
       </c>
       <c r="R14" t="n">
-        <v>6351145.464735172</v>
+        <v>6351144</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2385,24 +2200,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Yngelbo 10 cm. Boplats 1,5 m över marken i ek. Samma fina ekkrattskog med nära nog optimal succession.</t>
+          <t>Yngelbo 10 cm. Boplats 1,7 m över marken i ek. Samma fina ekkrattskog som föregående med rikligt inslag av kaprifol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2429,15 +2234,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98719918</v>
+        <v>98720044</v>
       </c>
       <c r="B15" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2474,7 +2274,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2485,14 +2285,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vä 27, Hl</t>
+          <t>Vä 30, Hl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>327566.2012430539</v>
+        <v>327602</v>
       </c>
       <c r="R15" t="n">
-        <v>6351137.239247059</v>
+        <v>6351146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2522,24 +2322,14 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hanbo 7 cm. Boplats 1,5 m över marken i ek med rikligt  inslag av kaprifol. Ung krattskog av ek, 2-3 m hög. En del närliggande överståndare av björk.</t>
+          <t>Yngelbo 10 cm. Boplats 1,5 m över marken i ek. Samma fina ekkrattskog med nära nog optimal succession.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2566,32 +2356,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114315821</v>
+        <v>98720169</v>
       </c>
       <c r="B16" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100084</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2599,22 +2384,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bua, Hl</t>
+          <t>Vä 31, Hl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>327707</v>
+        <v>327660</v>
       </c>
       <c r="R16" t="n">
-        <v>6350856</v>
+        <v>6351262</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2641,17 +2441,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fynd rapporterad efter NVI utförd vid Bua av Calluna AB oktober-november 2023</t>
+          <t>Hanbo 7 cm. Boplats 0,8 m över marken i ek. Sydvästbryn med björnbärssnår och 1,5-2 m höga småekar.  Överståndare av björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2666,31 +2466,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Calluna AB NVI JMN0117 Bua 2023</t>
-        </is>
-      </c>
+          <t>Boris Berglund, Tage Vowles</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122788734</v>
+        <v>98720256</v>
       </c>
       <c r="B17" t="n">
-        <v>56440</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2698,42 +2489,57 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208255</v>
+        <v>100084</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Varberg, Hl</t>
+          <t>Vä 32, Hl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>327621</v>
+        <v>327651</v>
       </c>
       <c r="R17" t="n">
-        <v>6351154</v>
+        <v>6351257</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2757,12 +2563,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Yngelbo 10 cm. Boplats 0,5 m över marken i ek. Sydvänt bryn med asp, ek, björnbär och björk. Även inslag av högvuxet gräs.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,22 +2582,705 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Boris Berglund, Tage Vowles</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>98720447</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vä 33, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>327645</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6351266</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förfallet hanbo. Boplats 1,4 m över marken i ek. Samma sydvästbryn som tidigare med asp, ek, björnbär och björk. Även inslag av högvuxet gräs.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Boris Berglund, Tage Vowles</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>98720521</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vä 34, Hl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>327488</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6351265</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Yngelbo 14 x 11 cm. Boplats 0,8 m över marken i ek. Slyrikt avsnitt i kraftledningsgata. Höjd 2-3 m bestående av ek, björk, en, brakved och björnbär.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Boris Berglund, Tage Vowles</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>95751366</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Härkulla, Hl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>327658</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6351029</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122788734</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>327621</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6351154</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Julius Stölzle</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Magnus Lundström</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16771162</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lingome, Hl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>327930</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6351008</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2014-10-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2014-10-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16455160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>107295</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221647</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mjukdån</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Galeopsis ladanum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lingome, nordost om, Hl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>327585</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6351252</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Sandig stig vid tidigare åker</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
